--- a/list.xlsx
+++ b/list.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\art-exhibition\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D215AAF-8C34-4483-9C26-720AEE746A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3A3A65-E781-4913-90AB-0FB5258BD086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2B79C24C-54B8-4002-83C1-CFF44F9FCFCA}"/>
   </bookViews>
@@ -1422,673 +1422,684 @@
     <t>artwork117.webp</t>
   </si>
   <si>
+    <t>artwork122.webp</t>
+  </si>
+  <si>
+    <t>artwork123.webp</t>
+  </si>
+  <si>
+    <t>artwork131.webp</t>
+  </si>
+  <si>
+    <t>artwork132.webp</t>
+  </si>
+  <si>
+    <t>artwork133.webp</t>
+  </si>
+  <si>
+    <t>artwork134.webp</t>
+  </si>
+  <si>
+    <t>artwork135.webp</t>
+  </si>
+  <si>
+    <t>artwork136.webp</t>
+  </si>
+  <si>
+    <t>artwork137.webp</t>
+  </si>
+  <si>
+    <t>artwork138.webp</t>
+  </si>
+  <si>
+    <t>artwork139.webp</t>
+  </si>
+  <si>
+    <t>artwork140.webp</t>
+  </si>
+  <si>
+    <t>artwork141.webp</t>
+  </si>
+  <si>
+    <t>artwork142.webp</t>
+  </si>
+  <si>
+    <t>artwork143.webp</t>
+  </si>
+  <si>
+    <t>artwork144.webp</t>
+  </si>
+  <si>
+    <t>artwork145.webp</t>
+  </si>
+  <si>
+    <t>artwork146.webp</t>
+  </si>
+  <si>
+    <t>artwork147.webp</t>
+  </si>
+  <si>
+    <t>artwork148.webp</t>
+  </si>
+  <si>
+    <t>artwork149.webp</t>
+  </si>
+  <si>
+    <t>artwork150.webp</t>
+  </si>
+  <si>
+    <t>artwork151.webp</t>
+  </si>
+  <si>
+    <t>artwork152.webp</t>
+  </si>
+  <si>
+    <t>artwork153.webp</t>
+  </si>
+  <si>
+    <t>artwork154.webp</t>
+  </si>
+  <si>
+    <t>artwork155.webp</t>
+  </si>
+  <si>
+    <t>artwork156.webp</t>
+  </si>
+  <si>
+    <t>artwork157.webp</t>
+  </si>
+  <si>
+    <t>artwork158.webp</t>
+  </si>
+  <si>
+    <t>artwork159.webp</t>
+  </si>
+  <si>
+    <t>artwork160.webp</t>
+  </si>
+  <si>
+    <t>artwork161.webp</t>
+  </si>
+  <si>
+    <t>artwork162.webp</t>
+  </si>
+  <si>
+    <t>artwork163.webp</t>
+  </si>
+  <si>
+    <t>artwork164.webp</t>
+  </si>
+  <si>
+    <t>artwork165.webp</t>
+  </si>
+  <si>
+    <t>artwork166.webp</t>
+  </si>
+  <si>
+    <t>artwork167.webp</t>
+  </si>
+  <si>
+    <t>artwork168.webp</t>
+  </si>
+  <si>
+    <t>artwork169.webp</t>
+  </si>
+  <si>
+    <t>artwork170.webp</t>
+  </si>
+  <si>
+    <t>artwork171.webp</t>
+  </si>
+  <si>
+    <t>artwork172.webp</t>
+  </si>
+  <si>
+    <t>artwork173.webp</t>
+  </si>
+  <si>
+    <t>artwork174.webp</t>
+  </si>
+  <si>
+    <t>artwork175.webp</t>
+  </si>
+  <si>
+    <t>artwork176.webp</t>
+  </si>
+  <si>
+    <t>artwork177.webp</t>
+  </si>
+  <si>
+    <t>artwork178.webp</t>
+  </si>
+  <si>
+    <t>artwork179.webp</t>
+  </si>
+  <si>
+    <t>artwork180.webp</t>
+  </si>
+  <si>
+    <t>artwork181.webp</t>
+  </si>
+  <si>
+    <t>artwork182.webp</t>
+  </si>
+  <si>
+    <t>artwork183.webp</t>
+  </si>
+  <si>
+    <t>artwork184.webp</t>
+  </si>
+  <si>
+    <t>artwork185.webp</t>
+  </si>
+  <si>
+    <t>artwork186.webp</t>
+  </si>
+  <si>
+    <t>artwork187.webp</t>
+  </si>
+  <si>
+    <t>artwork188.webp</t>
+  </si>
+  <si>
+    <t>artwork189.webp</t>
+  </si>
+  <si>
+    <t>artwork190.webp</t>
+  </si>
+  <si>
+    <t>artwork191.webp</t>
+  </si>
+  <si>
+    <t>artwork192.webp</t>
+  </si>
+  <si>
+    <t>artwork193.webp</t>
+  </si>
+  <si>
+    <t>artwork194.webp</t>
+  </si>
+  <si>
+    <t>artwork195.webp</t>
+  </si>
+  <si>
+    <t>artwork196.webp</t>
+  </si>
+  <si>
+    <t>artwork197.webp</t>
+  </si>
+  <si>
+    <t>artwork198.webp</t>
+  </si>
+  <si>
+    <t>artwork199.webp</t>
+  </si>
+  <si>
+    <t>artwork200.webp</t>
+  </si>
+  <si>
+    <t>artwork201.webp</t>
+  </si>
+  <si>
+    <t>artwork202.webp</t>
+  </si>
+  <si>
+    <t>artwork203.webp</t>
+  </si>
+  <si>
+    <t>artwork204.webp</t>
+  </si>
+  <si>
+    <t>artwork205.webp</t>
+  </si>
+  <si>
+    <t>artwork206.webp</t>
+  </si>
+  <si>
+    <t>artwork207.webp</t>
+  </si>
+  <si>
+    <t>artwork208.webp</t>
+  </si>
+  <si>
+    <t>artwork209.webp</t>
+  </si>
+  <si>
+    <t>artwork210.webp</t>
+  </si>
+  <si>
+    <t>artwork211.webp</t>
+  </si>
+  <si>
+    <t>artwork212.webp</t>
+  </si>
+  <si>
+    <t>artwork213.webp</t>
+  </si>
+  <si>
+    <t>artwork214.webp</t>
+  </si>
+  <si>
+    <t>artwork215.webp</t>
+  </si>
+  <si>
+    <t>artwork216.webp</t>
+  </si>
+  <si>
+    <t>artwork217.webp</t>
+  </si>
+  <si>
+    <t>artwork218.webp</t>
+  </si>
+  <si>
+    <t>artwork219.webp</t>
+  </si>
+  <si>
+    <t>artwork220.webp</t>
+  </si>
+  <si>
+    <t>artwork221.webp</t>
+  </si>
+  <si>
+    <t>artwork222.webp</t>
+  </si>
+  <si>
+    <t>artwork223.webp</t>
+  </si>
+  <si>
+    <t>artwork224.webp</t>
+  </si>
+  <si>
+    <t>artwork225.webp</t>
+  </si>
+  <si>
+    <t>artwork226.webp</t>
+  </si>
+  <si>
+    <t>artwork227.webp</t>
+  </si>
+  <si>
+    <t>artwork228.webp</t>
+  </si>
+  <si>
+    <t>artwork229.webp</t>
+  </si>
+  <si>
+    <t>artwork230.webp</t>
+  </si>
+  <si>
+    <t>artwork231.webp</t>
+  </si>
+  <si>
+    <t>artwork232.webp</t>
+  </si>
+  <si>
+    <t>artwork233.webp</t>
+  </si>
+  <si>
+    <t>artwork234.webp</t>
+  </si>
+  <si>
+    <t>artwork235.webp</t>
+  </si>
+  <si>
+    <t>artwork236.webp</t>
+  </si>
+  <si>
+    <t>artwork237.webp</t>
+  </si>
+  <si>
+    <t>artwork238.webp</t>
+  </si>
+  <si>
+    <t>artwork239.webp</t>
+  </si>
+  <si>
+    <t>artwork240.webp</t>
+  </si>
+  <si>
+    <t>artwork241.webp</t>
+  </si>
+  <si>
+    <t>artwork242.webp</t>
+  </si>
+  <si>
+    <t>artwork243.webp</t>
+  </si>
+  <si>
+    <t>artwork244.webp</t>
+  </si>
+  <si>
+    <t>artwork245.webp</t>
+  </si>
+  <si>
+    <t>artwork246.webp</t>
+  </si>
+  <si>
+    <t>artwork247.webp</t>
+  </si>
+  <si>
+    <t>artwork248.webp</t>
+  </si>
+  <si>
+    <t>artwork249.webp</t>
+  </si>
+  <si>
+    <t>artwork250.webp</t>
+  </si>
+  <si>
+    <t>artwork251.webp</t>
+  </si>
+  <si>
+    <t>artwork252.webp</t>
+  </si>
+  <si>
+    <t>artwork253.webp</t>
+  </si>
+  <si>
+    <t>artwork254.webp</t>
+  </si>
+  <si>
+    <t>artwork255.webp</t>
+  </si>
+  <si>
+    <t>artwork256.webp</t>
+  </si>
+  <si>
+    <t>artwork257.webp</t>
+  </si>
+  <si>
+    <t>artwork258.webp</t>
+  </si>
+  <si>
+    <t>artwork259.webp</t>
+  </si>
+  <si>
+    <t>artwork260.webp</t>
+  </si>
+  <si>
+    <t>artwork261.webp</t>
+  </si>
+  <si>
+    <t>artwork262.webp</t>
+  </si>
+  <si>
+    <t>artwork263.webp</t>
+  </si>
+  <si>
+    <t>artwork264.webp</t>
+  </si>
+  <si>
+    <t>artwork265.webp</t>
+  </si>
+  <si>
+    <t>artwork266.webp</t>
+  </si>
+  <si>
+    <t>artwork267.webp</t>
+  </si>
+  <si>
+    <t>artwork268.webp</t>
+  </si>
+  <si>
+    <t>artwork269.webp</t>
+  </si>
+  <si>
+    <t>artwork270.webp</t>
+  </si>
+  <si>
+    <t>artwork271.webp</t>
+  </si>
+  <si>
+    <t>artwork272.webp</t>
+  </si>
+  <si>
+    <t>artwork273.webp</t>
+  </si>
+  <si>
+    <t>artwork274.webp</t>
+  </si>
+  <si>
+    <t>artwork275.webp</t>
+  </si>
+  <si>
+    <t>artwork276.webp</t>
+  </si>
+  <si>
+    <t>artwork277.webp</t>
+  </si>
+  <si>
+    <t>artwork278.webp</t>
+  </si>
+  <si>
+    <t>artwork279.webp</t>
+  </si>
+  <si>
+    <t>artwork280.webp</t>
+  </si>
+  <si>
+    <t>artwork281.webp</t>
+  </si>
+  <si>
+    <t>artwork282.webp</t>
+  </si>
+  <si>
+    <t>artwork283.webp</t>
+  </si>
+  <si>
+    <t>artwork284.webp</t>
+  </si>
+  <si>
+    <t>artwork285.webp</t>
+  </si>
+  <si>
+    <t>artwork286.webp</t>
+  </si>
+  <si>
+    <t>artwork287.webp</t>
+  </si>
+  <si>
+    <t>artwork288.webp</t>
+  </si>
+  <si>
+    <t>artwork289.webp</t>
+  </si>
+  <si>
+    <t>artwork290.webp</t>
+  </si>
+  <si>
+    <t>artwork291.webp</t>
+  </si>
+  <si>
+    <t>artwork292.webp</t>
+  </si>
+  <si>
+    <t>artwork293.webp</t>
+  </si>
+  <si>
+    <t>artwork294.webp</t>
+  </si>
+  <si>
+    <t>artwork295.webp</t>
+  </si>
+  <si>
+    <t>artwork296.webp</t>
+  </si>
+  <si>
+    <t>artwork297.webp</t>
+  </si>
+  <si>
+    <t>artwork298.webp</t>
+  </si>
+  <si>
+    <t>artwork299.webp</t>
+  </si>
+  <si>
+    <t>artwork300.webp</t>
+  </si>
+  <si>
+    <t>artwork301.webp</t>
+  </si>
+  <si>
+    <t>artwork302.webp</t>
+  </si>
+  <si>
+    <t>artwork303.webp</t>
+  </si>
+  <si>
+    <t>artwork304.webp</t>
+  </si>
+  <si>
+    <t>artwork305.webp</t>
+  </si>
+  <si>
+    <t>artwork306.webp</t>
+  </si>
+  <si>
+    <t>artwork307.webp</t>
+  </si>
+  <si>
+    <t>artwork308.webp</t>
+  </si>
+  <si>
+    <t>artwork309.webp</t>
+  </si>
+  <si>
+    <t>artwork310.webp</t>
+  </si>
+  <si>
+    <t>artwork311.webp</t>
+  </si>
+  <si>
+    <t>artwork312.webp</t>
+  </si>
+  <si>
+    <t>artwork313.webp</t>
+  </si>
+  <si>
+    <t>artwork314.webp</t>
+  </si>
+  <si>
+    <t>artwork315.webp</t>
+  </si>
+  <si>
+    <t>artwork316.webp</t>
+  </si>
+  <si>
+    <t>artwork317.webp</t>
+  </si>
+  <si>
+    <t>artwork318.webp</t>
+  </si>
+  <si>
+    <t>artwork319.webp</t>
+  </si>
+  <si>
+    <t>artwork320.webp</t>
+  </si>
+  <si>
+    <t>artwork321.webp</t>
+  </si>
+  <si>
+    <t>artwork322.webp</t>
+  </si>
+  <si>
+    <t>artwork323.webp</t>
+  </si>
+  <si>
+    <t>artwork324.webp</t>
+  </si>
+  <si>
+    <t>artwork325.webp</t>
+  </si>
+  <si>
+    <t>artwork326.webp</t>
+  </si>
+  <si>
+    <t>artwork327.webp</t>
+  </si>
+  <si>
+    <t>artwork328.webp</t>
+  </si>
+  <si>
+    <t>artwork329.webp</t>
+  </si>
+  <si>
+    <t>ink</t>
+  </si>
+  <si>
+    <t>scenery</t>
+  </si>
+  <si>
+    <t>masterpiece</t>
+  </si>
+  <si>
+    <t>chinese</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>urban</t>
+  </si>
+  <si>
+    <t>food</t>
+  </si>
+  <si>
+    <t>healthy</t>
+  </si>
+  <si>
+    <t>school</t>
+  </si>
+  <si>
+    <t>animals</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
     <t>artwork118.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork119.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork120.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork121.webp</t>
-  </si>
-  <si>
-    <t>artwork122.webp</t>
-  </si>
-  <si>
-    <t>artwork123.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork124.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork125.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork126.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork127.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork128.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork129.webp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>artwork130.webp</t>
-  </si>
-  <si>
-    <t>artwork131.webp</t>
-  </si>
-  <si>
-    <t>artwork132.webp</t>
-  </si>
-  <si>
-    <t>artwork133.webp</t>
-  </si>
-  <si>
-    <t>artwork134.webp</t>
-  </si>
-  <si>
-    <t>artwork135.webp</t>
-  </si>
-  <si>
-    <t>artwork136.webp</t>
-  </si>
-  <si>
-    <t>artwork137.webp</t>
-  </si>
-  <si>
-    <t>artwork138.webp</t>
-  </si>
-  <si>
-    <t>artwork139.webp</t>
-  </si>
-  <si>
-    <t>artwork140.webp</t>
-  </si>
-  <si>
-    <t>artwork141.webp</t>
-  </si>
-  <si>
-    <t>artwork142.webp</t>
-  </si>
-  <si>
-    <t>artwork143.webp</t>
-  </si>
-  <si>
-    <t>artwork144.webp</t>
-  </si>
-  <si>
-    <t>artwork145.webp</t>
-  </si>
-  <si>
-    <t>artwork146.webp</t>
-  </si>
-  <si>
-    <t>artwork147.webp</t>
-  </si>
-  <si>
-    <t>artwork148.webp</t>
-  </si>
-  <si>
-    <t>artwork149.webp</t>
-  </si>
-  <si>
-    <t>artwork150.webp</t>
-  </si>
-  <si>
-    <t>artwork151.webp</t>
-  </si>
-  <si>
-    <t>artwork152.webp</t>
-  </si>
-  <si>
-    <t>artwork153.webp</t>
-  </si>
-  <si>
-    <t>artwork154.webp</t>
-  </si>
-  <si>
-    <t>artwork155.webp</t>
-  </si>
-  <si>
-    <t>artwork156.webp</t>
-  </si>
-  <si>
-    <t>artwork157.webp</t>
-  </si>
-  <si>
-    <t>artwork158.webp</t>
-  </si>
-  <si>
-    <t>artwork159.webp</t>
-  </si>
-  <si>
-    <t>artwork160.webp</t>
-  </si>
-  <si>
-    <t>artwork161.webp</t>
-  </si>
-  <si>
-    <t>artwork162.webp</t>
-  </si>
-  <si>
-    <t>artwork163.webp</t>
-  </si>
-  <si>
-    <t>artwork164.webp</t>
-  </si>
-  <si>
-    <t>artwork165.webp</t>
-  </si>
-  <si>
-    <t>artwork166.webp</t>
-  </si>
-  <si>
-    <t>artwork167.webp</t>
-  </si>
-  <si>
-    <t>artwork168.webp</t>
-  </si>
-  <si>
-    <t>artwork169.webp</t>
-  </si>
-  <si>
-    <t>artwork170.webp</t>
-  </si>
-  <si>
-    <t>artwork171.webp</t>
-  </si>
-  <si>
-    <t>artwork172.webp</t>
-  </si>
-  <si>
-    <t>artwork173.webp</t>
-  </si>
-  <si>
-    <t>artwork174.webp</t>
-  </si>
-  <si>
-    <t>artwork175.webp</t>
-  </si>
-  <si>
-    <t>artwork176.webp</t>
-  </si>
-  <si>
-    <t>artwork177.webp</t>
-  </si>
-  <si>
-    <t>artwork178.webp</t>
-  </si>
-  <si>
-    <t>artwork179.webp</t>
-  </si>
-  <si>
-    <t>artwork180.webp</t>
-  </si>
-  <si>
-    <t>artwork181.webp</t>
-  </si>
-  <si>
-    <t>artwork182.webp</t>
-  </si>
-  <si>
-    <t>artwork183.webp</t>
-  </si>
-  <si>
-    <t>artwork184.webp</t>
-  </si>
-  <si>
-    <t>artwork185.webp</t>
-  </si>
-  <si>
-    <t>artwork186.webp</t>
-  </si>
-  <si>
-    <t>artwork187.webp</t>
-  </si>
-  <si>
-    <t>artwork188.webp</t>
-  </si>
-  <si>
-    <t>artwork189.webp</t>
-  </si>
-  <si>
-    <t>artwork190.webp</t>
-  </si>
-  <si>
-    <t>artwork191.webp</t>
-  </si>
-  <si>
-    <t>artwork192.webp</t>
-  </si>
-  <si>
-    <t>artwork193.webp</t>
-  </si>
-  <si>
-    <t>artwork194.webp</t>
-  </si>
-  <si>
-    <t>artwork195.webp</t>
-  </si>
-  <si>
-    <t>artwork196.webp</t>
-  </si>
-  <si>
-    <t>artwork197.webp</t>
-  </si>
-  <si>
-    <t>artwork198.webp</t>
-  </si>
-  <si>
-    <t>artwork199.webp</t>
-  </si>
-  <si>
-    <t>artwork200.webp</t>
-  </si>
-  <si>
-    <t>artwork201.webp</t>
-  </si>
-  <si>
-    <t>artwork202.webp</t>
-  </si>
-  <si>
-    <t>artwork203.webp</t>
-  </si>
-  <si>
-    <t>artwork204.webp</t>
-  </si>
-  <si>
-    <t>artwork205.webp</t>
-  </si>
-  <si>
-    <t>artwork206.webp</t>
-  </si>
-  <si>
-    <t>artwork207.webp</t>
-  </si>
-  <si>
-    <t>artwork208.webp</t>
-  </si>
-  <si>
-    <t>artwork209.webp</t>
-  </si>
-  <si>
-    <t>artwork210.webp</t>
-  </si>
-  <si>
-    <t>artwork211.webp</t>
-  </si>
-  <si>
-    <t>artwork212.webp</t>
-  </si>
-  <si>
-    <t>artwork213.webp</t>
-  </si>
-  <si>
-    <t>artwork214.webp</t>
-  </si>
-  <si>
-    <t>artwork215.webp</t>
-  </si>
-  <si>
-    <t>artwork216.webp</t>
-  </si>
-  <si>
-    <t>artwork217.webp</t>
-  </si>
-  <si>
-    <t>artwork218.webp</t>
-  </si>
-  <si>
-    <t>artwork219.webp</t>
-  </si>
-  <si>
-    <t>artwork220.webp</t>
-  </si>
-  <si>
-    <t>artwork221.webp</t>
-  </si>
-  <si>
-    <t>artwork222.webp</t>
-  </si>
-  <si>
-    <t>artwork223.webp</t>
-  </si>
-  <si>
-    <t>artwork224.webp</t>
-  </si>
-  <si>
-    <t>artwork225.webp</t>
-  </si>
-  <si>
-    <t>artwork226.webp</t>
-  </si>
-  <si>
-    <t>artwork227.webp</t>
-  </si>
-  <si>
-    <t>artwork228.webp</t>
-  </si>
-  <si>
-    <t>artwork229.webp</t>
-  </si>
-  <si>
-    <t>artwork230.webp</t>
-  </si>
-  <si>
-    <t>artwork231.webp</t>
-  </si>
-  <si>
-    <t>artwork232.webp</t>
-  </si>
-  <si>
-    <t>artwork233.webp</t>
-  </si>
-  <si>
-    <t>artwork234.webp</t>
-  </si>
-  <si>
-    <t>artwork235.webp</t>
-  </si>
-  <si>
-    <t>artwork236.webp</t>
-  </si>
-  <si>
-    <t>artwork237.webp</t>
-  </si>
-  <si>
-    <t>artwork238.webp</t>
-  </si>
-  <si>
-    <t>artwork239.webp</t>
-  </si>
-  <si>
-    <t>artwork240.webp</t>
-  </si>
-  <si>
-    <t>artwork241.webp</t>
-  </si>
-  <si>
-    <t>artwork242.webp</t>
-  </si>
-  <si>
-    <t>artwork243.webp</t>
-  </si>
-  <si>
-    <t>artwork244.webp</t>
-  </si>
-  <si>
-    <t>artwork245.webp</t>
-  </si>
-  <si>
-    <t>artwork246.webp</t>
-  </si>
-  <si>
-    <t>artwork247.webp</t>
-  </si>
-  <si>
-    <t>artwork248.webp</t>
-  </si>
-  <si>
-    <t>artwork249.webp</t>
-  </si>
-  <si>
-    <t>artwork250.webp</t>
-  </si>
-  <si>
-    <t>artwork251.webp</t>
-  </si>
-  <si>
-    <t>artwork252.webp</t>
-  </si>
-  <si>
-    <t>artwork253.webp</t>
-  </si>
-  <si>
-    <t>artwork254.webp</t>
-  </si>
-  <si>
-    <t>artwork255.webp</t>
-  </si>
-  <si>
-    <t>artwork256.webp</t>
-  </si>
-  <si>
-    <t>artwork257.webp</t>
-  </si>
-  <si>
-    <t>artwork258.webp</t>
-  </si>
-  <si>
-    <t>artwork259.webp</t>
-  </si>
-  <si>
-    <t>artwork260.webp</t>
-  </si>
-  <si>
-    <t>artwork261.webp</t>
-  </si>
-  <si>
-    <t>artwork262.webp</t>
-  </si>
-  <si>
-    <t>artwork263.webp</t>
-  </si>
-  <si>
-    <t>artwork264.webp</t>
-  </si>
-  <si>
-    <t>artwork265.webp</t>
-  </si>
-  <si>
-    <t>artwork266.webp</t>
-  </si>
-  <si>
-    <t>artwork267.webp</t>
-  </si>
-  <si>
-    <t>artwork268.webp</t>
-  </si>
-  <si>
-    <t>artwork269.webp</t>
-  </si>
-  <si>
-    <t>artwork270.webp</t>
-  </si>
-  <si>
-    <t>artwork271.webp</t>
-  </si>
-  <si>
-    <t>artwork272.webp</t>
-  </si>
-  <si>
-    <t>artwork273.webp</t>
-  </si>
-  <si>
-    <t>artwork274.webp</t>
-  </si>
-  <si>
-    <t>artwork275.webp</t>
-  </si>
-  <si>
-    <t>artwork276.webp</t>
-  </si>
-  <si>
-    <t>artwork277.webp</t>
-  </si>
-  <si>
-    <t>artwork278.webp</t>
-  </si>
-  <si>
-    <t>artwork279.webp</t>
-  </si>
-  <si>
-    <t>artwork280.webp</t>
-  </si>
-  <si>
-    <t>artwork281.webp</t>
-  </si>
-  <si>
-    <t>artwork282.webp</t>
-  </si>
-  <si>
-    <t>artwork283.webp</t>
-  </si>
-  <si>
-    <t>artwork284.webp</t>
-  </si>
-  <si>
-    <t>artwork285.webp</t>
-  </si>
-  <si>
-    <t>artwork286.webp</t>
-  </si>
-  <si>
-    <t>artwork287.webp</t>
-  </si>
-  <si>
-    <t>artwork288.webp</t>
-  </si>
-  <si>
-    <t>artwork289.webp</t>
-  </si>
-  <si>
-    <t>artwork290.webp</t>
-  </si>
-  <si>
-    <t>artwork291.webp</t>
-  </si>
-  <si>
-    <t>artwork292.webp</t>
-  </si>
-  <si>
-    <t>artwork293.webp</t>
-  </si>
-  <si>
-    <t>artwork294.webp</t>
-  </si>
-  <si>
-    <t>artwork295.webp</t>
-  </si>
-  <si>
-    <t>artwork296.webp</t>
-  </si>
-  <si>
-    <t>artwork297.webp</t>
-  </si>
-  <si>
-    <t>artwork298.webp</t>
-  </si>
-  <si>
-    <t>artwork299.webp</t>
-  </si>
-  <si>
-    <t>artwork300.webp</t>
-  </si>
-  <si>
-    <t>artwork301.webp</t>
-  </si>
-  <si>
-    <t>artwork302.webp</t>
-  </si>
-  <si>
-    <t>artwork303.webp</t>
-  </si>
-  <si>
-    <t>artwork304.webp</t>
-  </si>
-  <si>
-    <t>artwork305.webp</t>
-  </si>
-  <si>
-    <t>artwork306.webp</t>
-  </si>
-  <si>
-    <t>artwork307.webp</t>
-  </si>
-  <si>
-    <t>artwork308.webp</t>
-  </si>
-  <si>
-    <t>artwork309.webp</t>
-  </si>
-  <si>
-    <t>artwork310.webp</t>
-  </si>
-  <si>
-    <t>artwork311.webp</t>
-  </si>
-  <si>
-    <t>artwork312.webp</t>
-  </si>
-  <si>
-    <t>artwork313.webp</t>
-  </si>
-  <si>
-    <t>artwork314.webp</t>
-  </si>
-  <si>
-    <t>artwork315.webp</t>
-  </si>
-  <si>
-    <t>artwork316.webp</t>
-  </si>
-  <si>
-    <t>artwork317.webp</t>
-  </si>
-  <si>
-    <t>artwork318.webp</t>
-  </si>
-  <si>
-    <t>artwork319.webp</t>
-  </si>
-  <si>
-    <t>artwork320.webp</t>
-  </si>
-  <si>
-    <t>artwork321.webp</t>
-  </si>
-  <si>
-    <t>artwork322.webp</t>
-  </si>
-  <si>
-    <t>artwork323.webp</t>
-  </si>
-  <si>
-    <t>artwork324.webp</t>
-  </si>
-  <si>
-    <t>artwork325.webp</t>
-  </si>
-  <si>
-    <t>artwork326.webp</t>
-  </si>
-  <si>
-    <t>artwork327.webp</t>
-  </si>
-  <si>
-    <t>artwork328.webp</t>
-  </si>
-  <si>
-    <t>artwork329.webp</t>
-  </si>
-  <si>
-    <t>ink</t>
-  </si>
-  <si>
-    <t>scenery</t>
-  </si>
-  <si>
-    <t>masterpiece</t>
-  </si>
-  <si>
-    <t>chinese</t>
-  </si>
-  <si>
-    <t>design</t>
-  </si>
-  <si>
-    <t>urban</t>
-  </si>
-  <si>
-    <t>food</t>
-  </si>
-  <si>
-    <t>healthy</t>
-  </si>
-  <si>
-    <t>school</t>
-  </si>
-  <si>
-    <t>animals</t>
-  </si>
-  <si>
-    <t>self</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2112,12 +2123,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -2134,11 +2151,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2502,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>289</v>
@@ -2525,7 +2545,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>290</v>
@@ -2548,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>291</v>
@@ -2571,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>292</v>
@@ -2594,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>293</v>
@@ -2617,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>294</v>
@@ -2640,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>295</v>
@@ -2663,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>296</v>
@@ -2686,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>297</v>
@@ -2709,7 +2729,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>298</v>
@@ -2732,7 +2752,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>299</v>
@@ -2755,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>300</v>
@@ -2778,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>301</v>
@@ -2801,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>302</v>
@@ -2824,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>303</v>
@@ -2847,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>304</v>
@@ -2870,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>305</v>
@@ -2893,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>306</v>
@@ -2916,7 +2936,7 @@
         <v>0</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>307</v>
@@ -2939,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>308</v>
@@ -2962,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>309</v>
@@ -2985,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>310</v>
@@ -3008,7 +3028,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>311</v>
@@ -3031,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>312</v>
@@ -3054,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>313</v>
@@ -3077,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>314</v>
@@ -3100,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>315</v>
@@ -3123,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>316</v>
@@ -3146,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>317</v>
@@ -3169,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>318</v>
@@ -3192,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>319</v>
@@ -3215,7 +3235,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>320</v>
@@ -3238,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>321</v>
@@ -3261,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>322</v>
@@ -3284,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>323</v>
@@ -3307,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>324</v>
@@ -3330,7 +3350,7 @@
         <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>325</v>
@@ -3353,7 +3373,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>326</v>
@@ -3376,7 +3396,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>327</v>
@@ -3399,7 +3419,7 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>328</v>
@@ -3422,7 +3442,7 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>329</v>
@@ -3445,7 +3465,7 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>330</v>
@@ -3468,7 +3488,7 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>331</v>
@@ -3491,7 +3511,7 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>332</v>
@@ -3514,7 +3534,7 @@
         <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>333</v>
@@ -3537,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>334</v>
@@ -3560,7 +3580,7 @@
         <v>8</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>335</v>
@@ -3583,7 +3603,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>336</v>
@@ -3606,7 +3626,7 @@
         <v>8</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>337</v>
@@ -3629,7 +3649,7 @@
         <v>8</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>338</v>
@@ -3652,7 +3672,7 @@
         <v>8</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>339</v>
@@ -3675,7 +3695,7 @@
         <v>8</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>340</v>
@@ -3698,7 +3718,7 @@
         <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>341</v>
@@ -3721,7 +3741,7 @@
         <v>11</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>342</v>
@@ -3744,7 +3764,7 @@
         <v>11</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>343</v>
@@ -3767,7 +3787,7 @@
         <v>11</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>344</v>
@@ -3790,7 +3810,7 @@
         <v>11</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>345</v>
@@ -3813,7 +3833,7 @@
         <v>11</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>346</v>
@@ -3836,7 +3856,7 @@
         <v>11</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>347</v>
@@ -3859,7 +3879,7 @@
         <v>11</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>348</v>
@@ -3882,7 +3902,7 @@
         <v>11</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>349</v>
@@ -3905,7 +3925,7 @@
         <v>11</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>350</v>
@@ -3928,7 +3948,7 @@
         <v>11</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>351</v>
@@ -3951,7 +3971,7 @@
         <v>11</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>352</v>
@@ -3974,7 +3994,7 @@
         <v>11</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>353</v>
@@ -3997,7 +4017,7 @@
         <v>11</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>354</v>
@@ -4020,7 +4040,7 @@
         <v>11</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>355</v>
@@ -4043,7 +4063,7 @@
         <v>11</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>356</v>
@@ -4066,7 +4086,7 @@
         <v>11</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>357</v>
@@ -4089,7 +4109,7 @@
         <v>11</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>358</v>
@@ -4112,7 +4132,7 @@
         <v>11</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>359</v>
@@ -4135,7 +4155,7 @@
         <v>11</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>360</v>
@@ -4158,7 +4178,7 @@
         <v>11</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>361</v>
@@ -4181,7 +4201,7 @@
         <v>15</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>362</v>
@@ -4204,7 +4224,7 @@
         <v>15</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>363</v>
@@ -4227,7 +4247,7 @@
         <v>15</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>364</v>
@@ -4250,7 +4270,7 @@
         <v>15</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>365</v>
@@ -4273,7 +4293,7 @@
         <v>15</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>366</v>
@@ -4296,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>367</v>
@@ -4319,7 +4339,7 @@
         <v>15</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>368</v>
@@ -4342,7 +4362,7 @@
         <v>15</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>369</v>
@@ -4365,7 +4385,7 @@
         <v>15</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>370</v>
@@ -4388,7 +4408,7 @@
         <v>15</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>371</v>
@@ -4411,7 +4431,7 @@
         <v>15</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>372</v>
@@ -4434,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>373</v>
@@ -4457,7 +4477,7 @@
         <v>15</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>374</v>
@@ -4480,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>375</v>
@@ -4503,7 +4523,7 @@
         <v>15</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>376</v>
@@ -4526,7 +4546,7 @@
         <v>15</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>377</v>
@@ -4549,7 +4569,7 @@
         <v>15</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>378</v>
@@ -4572,7 +4592,7 @@
         <v>15</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>379</v>
@@ -4595,7 +4615,7 @@
         <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>380</v>
@@ -4618,7 +4638,7 @@
         <v>15</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>381</v>
@@ -4641,7 +4661,7 @@
         <v>19</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>382</v>
@@ -4664,7 +4684,7 @@
         <v>19</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>383</v>
@@ -4687,7 +4707,7 @@
         <v>19</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>384</v>
@@ -4710,7 +4730,7 @@
         <v>19</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>385</v>
@@ -4733,7 +4753,7 @@
         <v>19</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>386</v>
@@ -4756,7 +4776,7 @@
         <v>19</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>387</v>
@@ -4779,7 +4799,7 @@
         <v>19</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>388</v>
@@ -4802,7 +4822,7 @@
         <v>19</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>389</v>
@@ -4825,7 +4845,7 @@
         <v>19</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>390</v>
@@ -4848,7 +4868,7 @@
         <v>19</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>391</v>
@@ -4871,7 +4891,7 @@
         <v>19</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>392</v>
@@ -4894,7 +4914,7 @@
         <v>19</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>393</v>
@@ -4917,7 +4937,7 @@
         <v>19</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>394</v>
@@ -4940,7 +4960,7 @@
         <v>19</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>395</v>
@@ -4963,7 +4983,7 @@
         <v>19</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>396</v>
@@ -4986,7 +5006,7 @@
         <v>19</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>397</v>
@@ -5009,7 +5029,7 @@
         <v>19</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>398</v>
@@ -5032,7 +5052,7 @@
         <v>19</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>399</v>
@@ -5055,7 +5075,7 @@
         <v>19</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>400</v>
@@ -5078,7 +5098,7 @@
         <v>19</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>401</v>
@@ -5101,7 +5121,7 @@
         <v>24</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>402</v>
@@ -5124,7 +5144,7 @@
         <v>24</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>403</v>
@@ -5147,7 +5167,7 @@
         <v>24</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>404</v>
@@ -5170,7 +5190,7 @@
         <v>24</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>405</v>
@@ -5180,95 +5200,95 @@
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" s="1">
+      <c r="A119" s="2">
         <v>118</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>406</v>
+      <c r="E119" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>619</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" s="1">
+      <c r="A120" s="2">
         <v>119</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="G120" s="1" t="s">
-        <v>407</v>
+      <c r="E120" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" s="1">
+      <c r="A121" s="2">
         <v>120</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>408</v>
+      <c r="E121" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" s="1">
+      <c r="A122" s="2">
         <v>121</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>409</v>
+      <c r="E122" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -5285,13 +5305,13 @@
         <v>24</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -5308,174 +5328,174 @@
         <v>24</v>
       </c>
       <c r="E124" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>125</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>126</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>127</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>128</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>129</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F130" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="F124" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="1">
-        <v>124</v>
-      </c>
-      <c r="B125" s="1" t="s">
+      <c r="G130" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>130</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D125" s="1" t="s">
+      <c r="C131" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D131" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E125" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="1">
-        <v>125</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="1">
-        <v>126</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="1">
-        <v>127</v>
-      </c>
-      <c r="B128" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="1">
-        <v>128</v>
-      </c>
-      <c r="B129" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="1">
-        <v>129</v>
-      </c>
-      <c r="B130" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="G130" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="1">
-        <v>130</v>
-      </c>
-      <c r="B131" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>625</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>418</v>
+      <c r="E131" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -5492,13 +5512,13 @@
         <v>24</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -5515,13 +5535,13 @@
         <v>24</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -5538,13 +5558,13 @@
         <v>28</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -5561,13 +5581,13 @@
         <v>28</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -5584,13 +5604,13 @@
         <v>28</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -5607,13 +5627,13 @@
         <v>28</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -5630,13 +5650,13 @@
         <v>28</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -5653,13 +5673,13 @@
         <v>28</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -5676,13 +5696,13 @@
         <v>28</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -5699,13 +5719,13 @@
         <v>28</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -5722,13 +5742,13 @@
         <v>28</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -5745,13 +5765,13 @@
         <v>28</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -5768,13 +5788,13 @@
         <v>28</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -5791,13 +5811,13 @@
         <v>28</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -5814,13 +5834,13 @@
         <v>28</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -5837,13 +5857,13 @@
         <v>28</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -5860,13 +5880,13 @@
         <v>28</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -5883,13 +5903,13 @@
         <v>28</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -5906,13 +5926,13 @@
         <v>28</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -5929,13 +5949,13 @@
         <v>28</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -5952,13 +5972,13 @@
         <v>28</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -5975,13 +5995,13 @@
         <v>28</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -5998,13 +6018,13 @@
         <v>28</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
@@ -6021,13 +6041,13 @@
         <v>28</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -6044,13 +6064,13 @@
         <v>28</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -6067,13 +6087,13 @@
         <v>28</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -6090,13 +6110,13 @@
         <v>28</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -6113,13 +6133,13 @@
         <v>28</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -6136,13 +6156,13 @@
         <v>28</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -6159,13 +6179,13 @@
         <v>28</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -6182,13 +6202,13 @@
         <v>28</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
@@ -6205,13 +6225,13 @@
         <v>28</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
@@ -6228,13 +6248,13 @@
         <v>28</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -6251,13 +6271,13 @@
         <v>28</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
@@ -6274,13 +6294,13 @@
         <v>28</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
@@ -6297,13 +6317,13 @@
         <v>28</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
@@ -6320,13 +6340,13 @@
         <v>28</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
@@ -6343,13 +6363,13 @@
         <v>28</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
@@ -6366,13 +6386,13 @@
         <v>28</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -6389,13 +6409,13 @@
         <v>28</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
@@ -6412,13 +6432,13 @@
         <v>28</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
@@ -6435,13 +6455,13 @@
         <v>28</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
@@ -6458,13 +6478,13 @@
         <v>28</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
@@ -6481,13 +6501,13 @@
         <v>28</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
@@ -6504,13 +6524,13 @@
         <v>28</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
@@ -6527,13 +6547,13 @@
         <v>28</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
@@ -6550,13 +6570,13 @@
         <v>28</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
@@ -6573,13 +6593,13 @@
         <v>28</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
@@ -6596,13 +6616,13 @@
         <v>28</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
@@ -6619,13 +6639,13 @@
         <v>28</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
@@ -6642,13 +6662,13 @@
         <v>28</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
@@ -6665,13 +6685,13 @@
         <v>28</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
@@ -6688,13 +6708,13 @@
         <v>28</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -6711,13 +6731,13 @@
         <v>34</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
@@ -6734,13 +6754,13 @@
         <v>34</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
@@ -6757,13 +6777,13 @@
         <v>34</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
@@ -6780,13 +6800,13 @@
         <v>34</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
@@ -6803,13 +6823,13 @@
         <v>34</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
@@ -6826,13 +6846,13 @@
         <v>34</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -6849,13 +6869,13 @@
         <v>34</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
@@ -6872,13 +6892,13 @@
         <v>34</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -6895,13 +6915,13 @@
         <v>34</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -6918,13 +6938,13 @@
         <v>34</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -6941,13 +6961,13 @@
         <v>34</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -6964,13 +6984,13 @@
         <v>34</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>483</v>
+        <v>472</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -6987,13 +7007,13 @@
         <v>34</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>484</v>
+        <v>473</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -7010,13 +7030,13 @@
         <v>34</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>485</v>
+        <v>474</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -7033,13 +7053,13 @@
         <v>34</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>486</v>
+        <v>475</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -7056,13 +7076,13 @@
         <v>34</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>487</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
@@ -7079,13 +7099,13 @@
         <v>34</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
@@ -7102,13 +7122,13 @@
         <v>34</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="G202" s="1" t="s">
-        <v>489</v>
+        <v>478</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
@@ -7125,13 +7145,13 @@
         <v>34</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
       <c r="G203" s="1" t="s">
-        <v>490</v>
+        <v>479</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
@@ -7148,13 +7168,13 @@
         <v>34</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
@@ -7171,13 +7191,13 @@
         <v>34</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F205" s="1" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
@@ -7194,13 +7214,13 @@
         <v>34</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F206" s="1" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
@@ -7217,13 +7237,13 @@
         <v>34</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
       <c r="G207" s="1" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
@@ -7240,13 +7260,13 @@
         <v>34</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>495</v>
+        <v>484</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
@@ -7263,13 +7283,13 @@
         <v>34</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
       <c r="G209" s="1" t="s">
-        <v>496</v>
+        <v>485</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
@@ -7286,13 +7306,13 @@
         <v>34</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>497</v>
+        <v>486</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
@@ -7309,13 +7329,13 @@
         <v>34</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F211" s="1" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
       <c r="G211" s="1" t="s">
-        <v>498</v>
+        <v>487</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
@@ -7332,13 +7352,13 @@
         <v>34</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
@@ -7355,13 +7375,13 @@
         <v>43</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
@@ -7378,13 +7398,13 @@
         <v>43</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="G214" s="1" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
@@ -7401,13 +7421,13 @@
         <v>43</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
@@ -7424,13 +7444,13 @@
         <v>43</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
       <c r="G216" s="1" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
@@ -7447,13 +7467,13 @@
         <v>43</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
       <c r="G217" s="1" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
@@ -7470,13 +7490,13 @@
         <v>43</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -7493,13 +7513,13 @@
         <v>43</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="G219" s="1" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
@@ -7516,13 +7536,13 @@
         <v>43</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
@@ -7539,13 +7559,13 @@
         <v>43</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
@@ -7562,13 +7582,13 @@
         <v>43</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
@@ -7585,13 +7605,13 @@
         <v>43</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
@@ -7608,13 +7628,13 @@
         <v>43</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
@@ -7631,13 +7651,13 @@
         <v>43</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
@@ -7654,13 +7674,13 @@
         <v>43</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
@@ -7677,13 +7697,13 @@
         <v>43</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
@@ -7700,13 +7720,13 @@
         <v>43</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
@@ -7723,13 +7743,13 @@
         <v>43</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
@@ -7746,13 +7766,13 @@
         <v>43</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
@@ -7769,13 +7789,13 @@
         <v>43</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
@@ -7792,13 +7812,13 @@
         <v>43</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
@@ -7815,13 +7835,13 @@
         <v>43</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
@@ -7838,13 +7858,13 @@
         <v>43</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>521</v>
+        <v>510</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
@@ -7861,13 +7881,13 @@
         <v>43</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
@@ -7884,13 +7904,13 @@
         <v>43</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>523</v>
+        <v>512</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
@@ -7907,13 +7927,13 @@
         <v>43</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
@@ -7930,13 +7950,13 @@
         <v>43</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
@@ -7953,13 +7973,13 @@
         <v>43</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>526</v>
+        <v>515</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
@@ -7976,13 +7996,13 @@
         <v>43</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>527</v>
+        <v>516</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
@@ -7999,13 +8019,13 @@
         <v>43</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
@@ -8022,13 +8042,13 @@
         <v>43</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>529</v>
+        <v>518</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
@@ -8045,13 +8065,13 @@
         <v>43</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>530</v>
+        <v>519</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
@@ -8068,13 +8088,13 @@
         <v>43</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>531</v>
+        <v>520</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
@@ -8091,13 +8111,13 @@
         <v>43</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
@@ -8114,13 +8134,13 @@
         <v>43</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
@@ -8137,13 +8157,13 @@
         <v>43</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
@@ -8160,13 +8180,13 @@
         <v>43</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
@@ -8183,13 +8203,13 @@
         <v>43</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -8206,13 +8226,13 @@
         <v>43</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -8229,13 +8249,13 @@
         <v>43</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -8252,13 +8272,13 @@
         <v>43</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -8275,13 +8295,13 @@
         <v>43</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -8298,13 +8318,13 @@
         <v>43</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -8321,13 +8341,13 @@
         <v>43</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -8344,13 +8364,13 @@
         <v>43</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -8367,13 +8387,13 @@
         <v>43</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -8390,13 +8410,13 @@
         <v>47</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -8413,13 +8433,13 @@
         <v>47</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -8436,13 +8456,13 @@
         <v>47</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -8459,13 +8479,13 @@
         <v>47</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -8482,13 +8502,13 @@
         <v>47</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -8505,13 +8525,13 @@
         <v>47</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -8528,13 +8548,13 @@
         <v>47</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -8551,13 +8571,13 @@
         <v>47</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -8574,13 +8594,13 @@
         <v>51</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -8597,13 +8617,13 @@
         <v>51</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -8620,13 +8640,13 @@
         <v>51</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -8643,13 +8663,13 @@
         <v>51</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -8666,13 +8686,13 @@
         <v>51</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -8689,13 +8709,13 @@
         <v>51</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -8712,13 +8732,13 @@
         <v>51</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F272" s="1" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
@@ -8735,13 +8755,13 @@
         <v>51</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F273" s="1" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
@@ -8758,13 +8778,13 @@
         <v>51</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F274" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
@@ -8781,13 +8801,13 @@
         <v>51</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
@@ -8804,13 +8824,13 @@
         <v>51</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
@@ -8827,13 +8847,13 @@
         <v>51</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="G277" s="1" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
@@ -8850,13 +8870,13 @@
         <v>51</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
@@ -8873,13 +8893,13 @@
         <v>60</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
@@ -8896,13 +8916,13 @@
         <v>60</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="G280" s="1" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -8919,13 +8939,13 @@
         <v>60</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -8942,13 +8962,13 @@
         <v>60</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -8965,13 +8985,13 @@
         <v>60</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -8988,13 +9008,13 @@
         <v>60</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -9011,13 +9031,13 @@
         <v>60</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -9034,13 +9054,13 @@
         <v>227</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -9057,13 +9077,13 @@
         <v>229</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -9080,13 +9100,13 @@
         <v>229</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -9103,13 +9123,13 @@
         <v>230</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -9126,13 +9146,13 @@
         <v>230</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
@@ -9149,13 +9169,13 @@
         <v>232</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="G291" s="1" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
@@ -9172,13 +9192,13 @@
         <v>232</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
@@ -9195,13 +9215,13 @@
         <v>230</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F293" s="1" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
@@ -9218,13 +9238,13 @@
         <v>230</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F294" s="1" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="G294" s="1" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -9241,13 +9261,13 @@
         <v>244</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -9264,13 +9284,13 @@
         <v>244</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -9287,13 +9307,13 @@
         <v>244</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -9310,13 +9330,13 @@
         <v>232</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F298" s="1" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
@@ -9333,13 +9353,13 @@
         <v>232</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F299" s="1" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="G299" s="1" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
@@ -9356,13 +9376,13 @@
         <v>229</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F300" s="1" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="G300" s="1" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
@@ -9379,13 +9399,13 @@
         <v>229</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F301" s="1" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="G301" s="1" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -9402,13 +9422,13 @@
         <v>229</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -9425,13 +9445,13 @@
         <v>230</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -9448,13 +9468,13 @@
         <v>244</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -9471,13 +9491,13 @@
         <v>244</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -9494,13 +9514,13 @@
         <v>244</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -9517,13 +9537,13 @@
         <v>227</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -9540,13 +9560,13 @@
         <v>229</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -9563,13 +9583,13 @@
         <v>230</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -9586,13 +9606,13 @@
         <v>230</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -9609,13 +9629,13 @@
         <v>230</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -9632,13 +9652,13 @@
         <v>230</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -9655,13 +9675,13 @@
         <v>230</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -9678,13 +9698,13 @@
         <v>244</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -9701,13 +9721,13 @@
         <v>232</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -9724,13 +9744,13 @@
         <v>230</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -9747,13 +9767,13 @@
         <v>230</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -9770,13 +9790,13 @@
         <v>230</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -9793,13 +9813,13 @@
         <v>244</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -9816,13 +9836,13 @@
         <v>230</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -9839,13 +9859,13 @@
         <v>230</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -9862,13 +9882,13 @@
         <v>230</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -9885,13 +9905,13 @@
         <v>244</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -9908,13 +9928,13 @@
         <v>244</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -9931,13 +9951,13 @@
         <v>275</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -9954,13 +9974,13 @@
         <v>275</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -9977,13 +9997,13 @@
         <v>229</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -10000,13 +10020,13 @@
         <v>244</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -10023,13 +10043,13 @@
         <v>227</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -10046,13 +10066,13 @@
         <v>244</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
